--- a/data/trans_camb/P0902-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P0902-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 10,45</t>
+          <t>-0,38; 10,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 7,52</t>
+          <t>-3,26; 7,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 3,87</t>
+          <t>-5,66; 4,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 21,24</t>
+          <t>6,03; 21,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 17,83</t>
+          <t>4,64; 18,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 3,23</t>
+          <t>-7,53; 2,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 13,59</t>
+          <t>5,1; 13,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 10,88</t>
+          <t>2,4; 10,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 1,64</t>
+          <t>-5,15; 1,89</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 163,81</t>
+          <t>-6,07; 175,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 130,95</t>
+          <t>-30,32; 123,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,61; 72,34</t>
+          <t>-50,57; 70,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,82; 205,49</t>
+          <t>31,47; 194,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,72; 166,23</t>
+          <t>26,13; 180,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,37; 32,91</t>
+          <t>-44,3; 27,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,39; 148,48</t>
+          <t>38,65; 143,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,19; 120,34</t>
+          <t>17,24; 114,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,28; 21,11</t>
+          <t>-37,93; 20,75</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 5,71</t>
+          <t>-2,39; 5,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,8</t>
+          <t>-4,59; 2,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 12,6</t>
+          <t>2,51; 12,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 6,43</t>
+          <t>-2,52; 6,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 3,89</t>
+          <t>-5,95; 3,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 12,43</t>
+          <t>3,72; 12,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 5,0</t>
+          <t>-1,17; 5,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 1,99</t>
+          <t>-4,05; 1,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 10,92</t>
+          <t>4,35; 10,96</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 76,77</t>
+          <t>-23,01; 73,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,92; 38,35</t>
+          <t>-39,52; 39,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,17; 176,25</t>
+          <t>22,22; 171,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 46,87</t>
+          <t>-14,09; 49,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 29,23</t>
+          <t>-31,17; 23,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,91; 87,57</t>
+          <t>19,23; 92,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 43,66</t>
+          <t>-8,56; 43,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,03; 17,38</t>
+          <t>-28,46; 17,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,89; 94,42</t>
+          <t>30,98; 99,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 11,55</t>
+          <t>2,63; 11,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 6,32</t>
+          <t>-1,11; 6,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 13,05</t>
+          <t>4,27; 13,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 10,86</t>
+          <t>0,19; 10,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 3,79</t>
+          <t>-5,91; 3,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 10,51</t>
+          <t>1,13; 10,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 9,69</t>
+          <t>2,75; 10,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 4,12</t>
+          <t>-2,26; 4,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 10,25</t>
+          <t>4,02; 10,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36,97; 373,6</t>
+          <t>33,87; 366,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 180,74</t>
+          <t>-20,59; 191,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57,44; 403,78</t>
+          <t>54,43; 443,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 118,65</t>
+          <t>0,6; 116,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 39,28</t>
+          <t>-42,07; 40,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,63; 112,07</t>
+          <t>7,01; 117,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,84; 141,78</t>
+          <t>26,16; 143,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 60,45</t>
+          <t>-23,23; 58,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,71; 152,36</t>
+          <t>37,82; 156,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,13; 16,35</t>
+          <t>6,94; 15,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,82; 17,56</t>
+          <t>8,77; 17,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,2; 19,26</t>
+          <t>9,53; 19,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,34; 23,58</t>
+          <t>12,16; 24,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,83; 21,8</t>
+          <t>10,01; 21,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 13,03</t>
+          <t>-3,2; 13,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,72; 18,2</t>
+          <t>11,05; 18,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,55; 18,32</t>
+          <t>10,43; 18,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,82; 14,79</t>
+          <t>4,19; 14,11</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>126,21; 647,06</t>
+          <t>126,1; 638,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>159,38; 741,33</t>
+          <t>153,89; 736,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>164,92; 824,33</t>
+          <t>177,54; 824,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66,24; 200,26</t>
+          <t>70,9; 200,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>57,06; 186,01</t>
+          <t>56,41; 188,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 104,3</t>
+          <t>-17,0; 109,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>104,12; 242,71</t>
+          <t>100,61; 248,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>98,75; 241,18</t>
+          <t>99,0; 241,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,11; 188,4</t>
+          <t>44,79; 181,51</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 9,72</t>
+          <t>-1,56; 9,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 5,68</t>
+          <t>-4,26; 5,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 4,18</t>
+          <t>-4,94; 4,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,77; 23,01</t>
+          <t>7,93; 22,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 8,73</t>
+          <t>-3,62; 9,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 5,34</t>
+          <t>-5,02; 5,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,05; 14,65</t>
+          <t>5,12; 14,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 5,7</t>
+          <t>-2,95; 5,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,81</t>
+          <t>-3,21; 3,71</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 187,7</t>
+          <t>-18,91; 199,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,17; 130,81</t>
+          <t>-43,68; 125,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 79,56</t>
+          <t>-49,7; 95,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47,52; 264,71</t>
+          <t>50,11; 287,75</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 107,4</t>
+          <t>-25,94; 125,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 67,42</t>
+          <t>-33,15; 73,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,95; 209,81</t>
+          <t>39,81; 189,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 77,49</t>
+          <t>-26,25; 66,74</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,52; 56,17</t>
+          <t>-28,14; 50,24</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 9,67</t>
+          <t>-0,22; 9,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,54; 11,64</t>
+          <t>0,32; 10,86</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 7,24</t>
+          <t>-1,48; 7,09</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 6,89</t>
+          <t>-5,54; 7,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 11,64</t>
+          <t>-2,35; 11,08</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 4,41</t>
+          <t>-6,55; 3,87</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 6,71</t>
+          <t>-1,75; 6,23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,43; 10,09</t>
+          <t>1,11; 9,47</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 4,21</t>
+          <t>-2,58; 4,02</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 157,2</t>
+          <t>-3,34; 171,01</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2,36; 190,43</t>
+          <t>1,77; 170,85</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 129,01</t>
+          <t>-16,19; 121,32</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,86; 53,98</t>
+          <t>-29,43; 54,5</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 83,3</t>
+          <t>-11,29; 86,5</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 34,14</t>
+          <t>-32,02; 30,54</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 64,38</t>
+          <t>-12,33; 60,48</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7,93; 90,74</t>
+          <t>6,49; 88,1</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-18,94; 40,21</t>
+          <t>-18,27; 38,79</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 1,12</t>
+          <t>-5,17; 1,03</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 2,72</t>
+          <t>-4,07; 2,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 6,86</t>
+          <t>-0,39; 6,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 5,48</t>
+          <t>-1,91; 5,8</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,79; 9,63</t>
+          <t>1,38; 9,69</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 9,1</t>
+          <t>-6,65; 9,28</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,62</t>
+          <t>-2,68; 2,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 5,41</t>
+          <t>-0,19; 5,41</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 6,61</t>
+          <t>-2,64; 6,53</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 14,87</t>
+          <t>-47,1; 13,34</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 34,4</t>
+          <t>-35,88; 35,02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 91,65</t>
+          <t>-3,26; 88,69</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 46,65</t>
+          <t>-12,22; 51,75</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>11,92; 85,6</t>
+          <t>9,24; 85,07</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 71,33</t>
+          <t>-44,31; 73,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 26,1</t>
+          <t>-20,4; 24,62</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 52,9</t>
+          <t>-2,02; 53,22</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 60,68</t>
+          <t>-21,12; 62,67</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 3,56</t>
+          <t>-2,99; 3,5</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-7,05; -1,63</t>
+          <t>-6,88; -1,46</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 2,41</t>
+          <t>-7,61; 2,51</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 4,28</t>
+          <t>-3,13; 4,83</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,74; -0,04</t>
+          <t>-7,44; 0,29</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 7,51</t>
+          <t>0,03; 7,46</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,39</t>
+          <t>-1,8; 2,94</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,32; -1,71</t>
+          <t>-6,13; -1,51</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 3,43</t>
+          <t>-5,17; 4,06</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 39,95</t>
+          <t>-26,18; 40,47</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-59,95; -19,76</t>
+          <t>-59,52; -17,71</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-63,82; 25,46</t>
+          <t>-60,6; 26,58</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 29,4</t>
+          <t>-17,45; 34,24</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-42,14; -0,29</t>
+          <t>-40,44; 1,4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 53,25</t>
+          <t>0,94; 53,0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 28,2</t>
+          <t>-12,72; 24,33</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-42,33; -12,53</t>
+          <t>-42,72; -12,01</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-39,08; 26,35</t>
+          <t>-35,91; 31,35</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,35</t>
+          <t>1,35; 4,5</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,43</t>
+          <t>-0,31; 2,66</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,4</t>
+          <t>0,85; 5,45</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,11</t>
+          <t>3,54; 7,2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,93</t>
+          <t>1,48; 5,04</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,03; 5,58</t>
+          <t>0,12; 5,57</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,33</t>
+          <t>3,03; 5,24</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,26</t>
+          <t>1,02; 3,32</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,05</t>
+          <t>1,76; 5,26</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>16,59; 58,76</t>
+          <t>15,22; 59,45</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 32,78</t>
+          <t>-3,55; 35,13</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>15,05; 71,21</t>
+          <t>13,07; 72,01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>23,56; 52,01</t>
+          <t>23,16; 52,19</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>9,47; 35,94</t>
+          <t>9,78; 36,37</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,66; 39,64</t>
+          <t>2,46; 40,78</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>24,65; 48,13</t>
+          <t>24,98; 48,38</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>7,96; 30,04</t>
+          <t>8,42; 30,88</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>13,69; 45,96</t>
+          <t>15,65; 48,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P0902-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P0902-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-1,29</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>-1,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,56</t>
+          <t>-1,48</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 10,24</t>
+          <t>-0,63; 10,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 7,25</t>
+          <t>-3,65; 6,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 4,02</t>
+          <t>-5,67; 3,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 21,11</t>
+          <t>6,92; 20,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 18,58</t>
+          <t>4,34; 17,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 2,76</t>
+          <t>-7,29; 3,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,1; 13,29</t>
+          <t>4,18; 13,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,65</t>
+          <t>1,89; 10,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 1,89</t>
+          <t>-5,02; 1,75</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-9,81%</t>
+          <t>-14,92%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-16,83%</t>
+          <t>-13,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-14,22%</t>
+          <t>-13,43%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 175,68</t>
+          <t>-7,81; 167,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,32; 123,4</t>
+          <t>-31,9; 115,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,57; 70,28</t>
+          <t>-50,44; 48,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,47; 194,22</t>
+          <t>38,56; 201,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,13; 180,93</t>
+          <t>25,81; 175,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,3; 27,09</t>
+          <t>-41,47; 33,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,65; 143,67</t>
+          <t>32,22; 146,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,24; 114,6</t>
+          <t>15,7; 116,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 20,75</t>
+          <t>-38,18; 19,57</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,78</t>
+          <t>8,33</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,04</t>
+          <t>7,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,86</t>
+          <t>7,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 5,4</t>
+          <t>-2,42; 5,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 2,71</t>
+          <t>-4,41; 2,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 12,52</t>
+          <t>3,24; 12,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 6,83</t>
+          <t>-3,35; 6,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 3,2</t>
+          <t>-5,82; 3,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 12,86</t>
+          <t>3,02; 11,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,05</t>
+          <t>-1,38; 5,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 1,89</t>
+          <t>-3,84; 1,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 10,96</t>
+          <t>4,54; 11,1</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 73,09</t>
+          <t>-23,52; 77,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,52; 39,79</t>
+          <t>-41,2; 33,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,22; 171,39</t>
+          <t>29,4; 168,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 49,17</t>
+          <t>-17,67; 49,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 23,22</t>
+          <t>-31,84; 22,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,23; 92,58</t>
+          <t>15,79; 90,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 43,5</t>
+          <t>-9,86; 44,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 17,3</t>
+          <t>-27,46; 17,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,98; 99,46</t>
+          <t>31,8; 99,94</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,65</t>
+          <t>8,27</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,77</t>
+          <t>5,32</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>6,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,6</t>
+          <t>2,5; 11,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 6,28</t>
+          <t>-0,79; 6,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,27; 13,05</t>
+          <t>4,22; 12,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 10,97</t>
+          <t>-0,25; 10,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 3,82</t>
+          <t>-5,87; 4,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,68</t>
+          <t>0,45; 9,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 10,1</t>
+          <t>2,5; 9,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 4,03</t>
+          <t>-2,75; 3,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 10,53</t>
+          <t>3,47; 9,87</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183,86%</t>
+          <t>175,74%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>81,45%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,87; 366,31</t>
+          <t>32,09; 338,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 191,01</t>
+          <t>-14,77; 226,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54,43; 443,82</t>
+          <t>58,2; 391,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 116,3</t>
+          <t>-2,72; 109,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,07; 40,54</t>
+          <t>-43,06; 42,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,01; 117,44</t>
+          <t>0,64; 106,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,16; 143,68</t>
+          <t>23,21; 145,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,23; 58,6</t>
+          <t>-27,61; 58,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,82; 156,3</t>
+          <t>33,64; 144,9</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14,22</t>
+          <t>13,17</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,86</t>
+          <t>10,63</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>12,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 15,45</t>
+          <t>7,61; 15,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,77; 17,79</t>
+          <t>8,74; 17,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,53; 19,71</t>
+          <t>8,87; 18,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,16; 24,2</t>
+          <t>12,41; 23,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,01; 21,89</t>
+          <t>10,0; 22,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 13,45</t>
+          <t>5,4; 15,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,05; 18,58</t>
+          <t>11,07; 18,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,43; 18,34</t>
+          <t>10,44; 18,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 14,11</t>
+          <t>8,42; 15,6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>382,1%</t>
+          <t>353,98%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>112,07%</t>
+          <t>132,85%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>126,1; 638,09</t>
+          <t>131,73; 620,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>153,89; 736,4</t>
+          <t>150,54; 711,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>177,54; 824,08</t>
+          <t>159,03; 771,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70,9; 200,26</t>
+          <t>68,86; 202,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>56,41; 188,96</t>
+          <t>59,12; 189,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 109,71</t>
+          <t>32,37; 140,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100,61; 248,97</t>
+          <t>103,79; 239,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>99,0; 241,36</t>
+          <t>98,68; 239,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>44,79; 181,51</t>
+          <t>76,23; 204,28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,45</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>-0,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 9,79</t>
+          <t>-1,6; 9,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 5,94</t>
+          <t>-4,76; 5,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 4,11</t>
+          <t>-5,56; 3,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,93; 22,87</t>
+          <t>6,93; 22,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 9,57</t>
+          <t>-4,42; 8,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 5,73</t>
+          <t>-5,56; 5,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,12; 14,49</t>
+          <t>5,18; 14,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 5,2</t>
+          <t>-2,41; 5,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 3,71</t>
+          <t>-3,84; 3,09</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-6,09%</t>
+          <t>-12,34%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>-2,4%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 199,34</t>
+          <t>-18,15; 181,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 125,13</t>
+          <t>-48,67; 112,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 95,44</t>
+          <t>-54,99; 81,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50,11; 287,75</t>
+          <t>40,69; 266,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 125,29</t>
+          <t>-29,27; 107,01</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 73,87</t>
+          <t>-36,26; 76,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,81; 189,24</t>
+          <t>44,72; 196,48</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 66,74</t>
+          <t>-20,85; 82,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 50,24</t>
+          <t>-32,93; 44,24</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>2,71</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-1,08</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,73</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 9,66</t>
+          <t>-0,23; 10,14</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,32; 10,86</t>
+          <t>0,92; 11,61</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 7,09</t>
+          <t>-1,67; 6,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 7,04</t>
+          <t>-6,03; 6,44</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 11,08</t>
+          <t>-1,86; 11,39</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 3,87</t>
+          <t>-6,85; 3,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 6,23</t>
+          <t>-1,76; 6,35</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,47</t>
+          <t>0,76; 9,66</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 4,02</t>
+          <t>-3,01; 3,94</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-5,91%</t>
+          <t>-6,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 171,01</t>
+          <t>-6,13; 167,63</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1,77; 170,85</t>
+          <t>5,51; 196,83</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 121,32</t>
+          <t>-16,24; 123,29</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 54,5</t>
+          <t>-30,27; 50,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 86,5</t>
+          <t>-10,37; 85,43</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-32,02; 30,54</t>
+          <t>-34,14; 30,42</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 60,48</t>
+          <t>-12,71; 59,15</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6,49; 88,1</t>
+          <t>4,35; 91,78</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 38,79</t>
+          <t>-21,73; 37,1</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,16</t>
+          <t>2,94</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>8,86</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,31</t>
+          <t>6,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 1,03</t>
+          <t>-5,36; 1,1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 2,7</t>
+          <t>-4,29; 2,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 6,73</t>
+          <t>-0,44; 6,68</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 5,8</t>
+          <t>-2,32; 5,24</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,38; 9,69</t>
+          <t>1,22; 9,38</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 9,28</t>
+          <t>4,96; 12,6</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,41</t>
+          <t>-2,91; 2,27</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 5,41</t>
+          <t>-0,32; 5,36</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,53</t>
+          <t>3,76; 9,07</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-47,1; 13,34</t>
+          <t>-46,92; 14,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 35,02</t>
+          <t>-39,42; 34,83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 88,69</t>
+          <t>-4,88; 90,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 51,75</t>
+          <t>-14,87; 44,08</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,24; 85,07</t>
+          <t>7,76; 79,57</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 73,14</t>
+          <t>30,74; 108,9</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 24,62</t>
+          <t>-22,96; 22,81</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 53,22</t>
+          <t>-2,12; 54,19</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,12; 62,67</t>
+          <t>28,7; 90,75</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,8</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>2,02</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 3,5</t>
+          <t>-2,9; 3,58</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,88; -1,46</t>
+          <t>-6,87; -1,32</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 2,51</t>
+          <t>-1,87; 4,25</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 4,83</t>
+          <t>-2,96; 4,53</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 0,29</t>
+          <t>-7,49; -0,01</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,03; 7,46</t>
+          <t>-0,32; 7,2</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,94</t>
+          <t>-1,85; 3,0</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,13; -1,51</t>
+          <t>-6,41; -1,6</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 4,06</t>
+          <t>-0,29; 4,37</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-16,36%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 40,47</t>
+          <t>-24,25; 41,77</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-59,52; -17,71</t>
+          <t>-59,36; -16,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-60,6; 26,58</t>
+          <t>-16,78; 49,26</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-17,45; 34,24</t>
+          <t>-16,43; 30,64</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 1,4</t>
+          <t>-40,74; -0,12</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,94; 53,0</t>
+          <t>-2,77; 49,1</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 24,33</t>
+          <t>-12,96; 24,65</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-42,72; -12,01</t>
+          <t>-43,09; -11,63</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-35,91; 31,35</t>
+          <t>-1,61; 37,18</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>4,31</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>4,73</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,5</t>
+          <t>1,44; 4,26</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,66</t>
+          <t>-0,26; 2,39</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,45</t>
+          <t>2,83; 5,7</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,2</t>
+          <t>3,38; 7,02</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,48; 5,04</t>
+          <t>1,27; 4,98</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,57</t>
+          <t>3,38; 6,61</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,24</t>
+          <t>2,93; 5,32</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,32</t>
+          <t>1,01; 3,37</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,26</t>
+          <t>3,61; 5,83</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>15,22; 59,45</t>
+          <t>15,92; 55,59</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 35,13</t>
+          <t>-2,93; 31,85</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>13,07; 72,01</t>
+          <t>32,01; 76,24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>23,16; 52,19</t>
+          <t>21,89; 51,02</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>9,78; 36,37</t>
+          <t>7,98; 36,11</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,46; 40,78</t>
+          <t>21,64; 47,85</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>24,98; 48,38</t>
+          <t>24,18; 48,43</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>8,42; 30,88</t>
+          <t>7,97; 30,45</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>15,65; 48,38</t>
+          <t>30,11; 53,65</t>
         </is>
       </c>
     </row>
